--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124190637</v>
+        <v>124189769</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637893</v>
+        <v>638030</v>
       </c>
       <c r="R2" t="n">
-        <v>6665652</v>
+        <v>6665602</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -919,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124189300</v>
+        <v>124232392</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638050</v>
+        <v>638011</v>
       </c>
       <c r="R4" t="n">
-        <v>6665625</v>
+        <v>6665601</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,24 +994,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124232011</v>
+        <v>124204041</v>
       </c>
       <c r="B5" t="n">
         <v>95551</v>
@@ -1076,7 +1059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1093,14 +1076,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638028</v>
+        <v>637921</v>
       </c>
       <c r="R5" t="n">
-        <v>6665609</v>
+        <v>6665671</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,14 +1113,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På murken stubbe i granskog</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189873</v>
+        <v>124205123</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1170,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1205,17 +1198,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638016</v>
+        <v>637929</v>
       </c>
       <c r="R6" t="n">
-        <v>6665594</v>
+        <v>6665530</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,12 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124232392</v>
+        <v>124209310</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,45 +1287,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638011</v>
+        <v>638018</v>
       </c>
       <c r="R7" t="n">
-        <v>6665601</v>
+        <v>6665626</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,18 +1348,32 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>9 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1394,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124204041</v>
+        <v>124232011</v>
       </c>
       <c r="B8" t="n">
         <v>95551</v>
@@ -1429,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1446,14 +1444,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637921</v>
+        <v>638028</v>
       </c>
       <c r="R8" t="n">
-        <v>6665671</v>
+        <v>6665609</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1483,24 +1481,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124205123</v>
+        <v>124189873</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,25 +1528,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1568,17 +1556,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637929</v>
+        <v>638016</v>
       </c>
       <c r="R9" t="n">
-        <v>6665530</v>
+        <v>6665594</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1595,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1605,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,7 +1638,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124204400</v>
+        <v>124190637</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1689,13 +1682,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637987</v>
+        <v>637893</v>
       </c>
       <c r="R10" t="n">
-        <v>6665598</v>
+        <v>6665652</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1724,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1734,12 +1727,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124209310</v>
+        <v>124204400</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1801,16 +1794,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638018</v>
+        <v>637987</v>
       </c>
       <c r="R11" t="n">
-        <v>6665626</v>
+        <v>6665598</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1842,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1852,12 +1849,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,6 +1863,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1884,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124189769</v>
+        <v>124189300</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,35 +1894,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1932,13 +1926,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638030</v>
+        <v>638050</v>
       </c>
       <c r="R12" t="n">
-        <v>6665602</v>
+        <v>6665625</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1967,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1977,7 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,6 +1985,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189769</v>
+        <v>124189300</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638030</v>
+        <v>638050</v>
       </c>
       <c r="R2" t="n">
-        <v>6665602</v>
+        <v>6665625</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +778,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124205801</v>
+        <v>124204041</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,45 +809,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637878</v>
+        <v>637921</v>
       </c>
       <c r="R3" t="n">
-        <v>6665615</v>
+        <v>6665671</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124232392</v>
+        <v>124190637</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +943,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638011</v>
+        <v>637893</v>
       </c>
       <c r="R4" t="n">
-        <v>6665601</v>
+        <v>6665652</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,9 +1008,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124204041</v>
+        <v>124209310</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,57 +1065,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637921</v>
+        <v>638018</v>
       </c>
       <c r="R5" t="n">
-        <v>6665671</v>
+        <v>6665626</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1138,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1152,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1158,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124205123</v>
+        <v>124189769</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,41 +1186,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637929</v>
+        <v>638030</v>
       </c>
       <c r="R6" t="n">
-        <v>6665530</v>
+        <v>6665602</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1263,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1272,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124209310</v>
+        <v>124204400</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1309,16 +1324,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638018</v>
+        <v>637987</v>
       </c>
       <c r="R7" t="n">
-        <v>6665626</v>
+        <v>6665598</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1350,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,6 +1393,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124232011</v>
+        <v>124205801</v>
       </c>
       <c r="B8" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,42 +1424,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1448,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638028</v>
+        <v>637878</v>
       </c>
       <c r="R8" t="n">
-        <v>6665609</v>
+        <v>6665615</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,14 +1489,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På murken stubbe i granskog</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124189873</v>
+        <v>124232392</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,25 +1546,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1560,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638016</v>
+        <v>638011</v>
       </c>
       <c r="R9" t="n">
-        <v>6665594</v>
+        <v>6665601</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1593,24 +1611,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1641,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124190637</v>
+        <v>124189873</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1682,10 +1685,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637893</v>
+        <v>638016</v>
       </c>
       <c r="R10" t="n">
-        <v>6665652</v>
+        <v>6665594</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1717,7 +1720,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,12 +1730,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124204400</v>
+        <v>124232011</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,30 +1775,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1804,13 +1819,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637987</v>
+        <v>638028</v>
       </c>
       <c r="R11" t="n">
-        <v>6665598</v>
+        <v>6665609</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,24 +1852,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124189300</v>
+        <v>124205123</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1894,25 +1899,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1922,14 +1927,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638050</v>
+        <v>637929</v>
       </c>
       <c r="R12" t="n">
-        <v>6665625</v>
+        <v>6665530</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1961,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189300</v>
+        <v>124204041</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638050</v>
+        <v>637921</v>
       </c>
       <c r="R2" t="n">
-        <v>6665625</v>
+        <v>6665671</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +776,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124204041</v>
+        <v>124189769</v>
       </c>
       <c r="B3" t="n">
-        <v>95551</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,57 +821,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637921</v>
+        <v>638030</v>
       </c>
       <c r="R3" t="n">
-        <v>6665671</v>
+        <v>6665602</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +911,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -931,7 +929,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190637</v>
+        <v>124189873</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -975,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637893</v>
+        <v>638016</v>
       </c>
       <c r="R4" t="n">
-        <v>6665652</v>
+        <v>6665594</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1010,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,12 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1051,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124209310</v>
+        <v>124190637</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1087,19 +1085,23 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638018</v>
+        <v>637893</v>
       </c>
       <c r="R5" t="n">
-        <v>6665626</v>
+        <v>6665652</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,6 +1154,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1170,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189769</v>
+        <v>124205123</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>96354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,45 +1189,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638030</v>
+        <v>637929</v>
       </c>
       <c r="R6" t="n">
-        <v>6665602</v>
+        <v>6665530</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,6 +1271,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124204400</v>
+        <v>124189300</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637987</v>
+        <v>638050</v>
       </c>
       <c r="R7" t="n">
-        <v>6665598</v>
+        <v>6665625</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124205801</v>
+        <v>124209310</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1446,20 +1446,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637878</v>
+        <v>638018</v>
       </c>
       <c r="R8" t="n">
-        <v>6665615</v>
+        <v>6665626</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1491,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1511,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1534,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124232392</v>
+        <v>124204400</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,25 +1541,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,13 +1573,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638011</v>
+        <v>637987</v>
       </c>
       <c r="R9" t="n">
-        <v>6665601</v>
+        <v>6665598</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,9 +1606,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124189873</v>
+        <v>124205801</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1685,13 +1695,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638016</v>
+        <v>637878</v>
       </c>
       <c r="R10" t="n">
-        <v>6665594</v>
+        <v>6665615</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1720,7 +1730,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1730,12 +1740,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1887,7 +1897,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124205123</v>
+        <v>124232392</v>
       </c>
       <c r="B12" t="n">
         <v>96354</v>
@@ -1927,17 +1937,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637929</v>
+        <v>638011</v>
       </c>
       <c r="R12" t="n">
-        <v>6665530</v>
+        <v>6665601</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,19 +1974,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124204041</v>
+        <v>124189873</v>
       </c>
       <c r="B2" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637921</v>
+        <v>638016</v>
       </c>
       <c r="R2" t="n">
-        <v>6665671</v>
+        <v>6665594</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124189769</v>
+        <v>124232011</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>95551</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,35 +809,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,13 +853,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638030</v>
+        <v>638028</v>
       </c>
       <c r="R3" t="n">
-        <v>6665602</v>
+        <v>6665609</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,19 +886,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,7 +921,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124189873</v>
+        <v>124204400</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -973,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638016</v>
+        <v>637987</v>
       </c>
       <c r="R4" t="n">
-        <v>6665594</v>
+        <v>6665598</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124190637</v>
+        <v>124209310</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1085,23 +1077,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637893</v>
+        <v>638018</v>
       </c>
       <c r="R5" t="n">
-        <v>6665652</v>
+        <v>6665626</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1128,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124205123</v>
+        <v>124232392</v>
       </c>
       <c r="B6" t="n">
         <v>96354</v>
@@ -1213,17 +1200,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637929</v>
+        <v>638011</v>
       </c>
       <c r="R6" t="n">
-        <v>6665530</v>
+        <v>6665601</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,19 +1237,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1412,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124209310</v>
+        <v>124204041</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,41 +1401,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638018</v>
+        <v>637921</v>
       </c>
       <c r="R8" t="n">
-        <v>6665626</v>
+        <v>6665671</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1490,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1504,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1529,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124204400</v>
+        <v>124190637</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1573,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637987</v>
+        <v>637893</v>
       </c>
       <c r="R9" t="n">
-        <v>6665598</v>
+        <v>6665652</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1608,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,12 +1612,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1773,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124232011</v>
+        <v>124205123</v>
       </c>
       <c r="B11" t="n">
-        <v>95551</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,57 +1779,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638028</v>
+        <v>637929</v>
       </c>
       <c r="R11" t="n">
-        <v>6665609</v>
+        <v>6665530</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1862,14 +1844,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På murken stubbe i granskog</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124232392</v>
+        <v>124189769</v>
       </c>
       <c r="B12" t="n">
-        <v>96354</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1913,27 +1900,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1941,10 +1932,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638011</v>
+        <v>638030</v>
       </c>
       <c r="R12" t="n">
-        <v>6665601</v>
+        <v>6665602</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1974,18 +1965,27 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189873</v>
+        <v>124190637</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638016</v>
+        <v>637893</v>
       </c>
       <c r="R2" t="n">
-        <v>6665594</v>
+        <v>6665652</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124232011</v>
+        <v>124232392</v>
       </c>
       <c r="B3" t="n">
-        <v>95551</v>
+        <v>96354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,42 +809,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -853,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638028</v>
+        <v>638011</v>
       </c>
       <c r="R3" t="n">
-        <v>6665609</v>
+        <v>6665601</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124204400</v>
+        <v>124209310</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -955,20 +938,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637987</v>
+        <v>638018</v>
       </c>
       <c r="R4" t="n">
-        <v>6665598</v>
+        <v>6665626</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1000,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1003,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1043,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124209310</v>
+        <v>124205123</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,38 +1033,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638018</v>
+        <v>637929</v>
       </c>
       <c r="R5" t="n">
-        <v>6665626</v>
+        <v>6665530</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1118,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>9 bladrosetter</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,6 +1119,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1160,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124232392</v>
+        <v>124189769</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,27 +1154,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638011</v>
+        <v>638030</v>
       </c>
       <c r="R6" t="n">
-        <v>6665601</v>
+        <v>6665602</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1237,18 +1219,27 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124189300</v>
+        <v>124205801</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1311,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638050</v>
+        <v>637878</v>
       </c>
       <c r="R7" t="n">
-        <v>6665625</v>
+        <v>6665615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1346,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1347,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124204041</v>
+        <v>124189873</v>
       </c>
       <c r="B8" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,57 +1392,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637921</v>
+        <v>638016</v>
       </c>
       <c r="R8" t="n">
-        <v>6665671</v>
+        <v>6665594</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124190637</v>
+        <v>124232011</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,30 +1514,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1567,13 +1558,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637893</v>
+        <v>638028</v>
       </c>
       <c r="R9" t="n">
-        <v>6665652</v>
+        <v>6665609</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1600,24 +1591,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124205801</v>
+        <v>124189300</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1689,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637878</v>
+        <v>638050</v>
       </c>
       <c r="R10" t="n">
-        <v>6665615</v>
+        <v>6665625</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1724,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1734,12 +1715,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124205123</v>
+        <v>124204041</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>95551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,45 +1760,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637929</v>
+        <v>637921</v>
       </c>
       <c r="R11" t="n">
-        <v>6665530</v>
+        <v>6665671</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1846,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1856,7 +1849,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124189769</v>
+        <v>124204400</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,35 +1894,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1932,13 +1926,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638030</v>
+        <v>637987</v>
       </c>
       <c r="R12" t="n">
-        <v>6665602</v>
+        <v>6665598</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1967,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1977,7 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,6 +1985,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2001,6 +2001,362 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124698226</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nötmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>638166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6665714</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124697608</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nötmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>638131</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6665719</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124696996</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nötmossen, norr om, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>638100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6665721</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124190637</v>
+        <v>124205123</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +715,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637893</v>
+        <v>637929</v>
       </c>
       <c r="R2" t="n">
-        <v>6665652</v>
+        <v>6665530</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124209310</v>
+        <v>124205801</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -938,16 +933,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638018</v>
+        <v>637878</v>
       </c>
       <c r="R4" t="n">
-        <v>6665626</v>
+        <v>6665615</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,6 +1002,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124205123</v>
+        <v>124189769</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,41 +1037,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637929</v>
+        <v>638030</v>
       </c>
       <c r="R5" t="n">
-        <v>6665530</v>
+        <v>6665602</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189769</v>
+        <v>124204041</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,49 +1153,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638030</v>
+        <v>637921</v>
       </c>
       <c r="R6" t="n">
-        <v>6665602</v>
+        <v>6665671</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,6 +1256,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124205801</v>
+        <v>124190637</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1302,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637878</v>
+        <v>637893</v>
       </c>
       <c r="R7" t="n">
-        <v>6665615</v>
+        <v>6665652</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,12 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124189873</v>
+        <v>124204400</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1424,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638016</v>
+        <v>637987</v>
       </c>
       <c r="R8" t="n">
-        <v>6665594</v>
+        <v>6665598</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124232011</v>
+        <v>124209310</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,57 +1531,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638028</v>
+        <v>638018</v>
       </c>
       <c r="R9" t="n">
-        <v>6665609</v>
+        <v>6665626</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,14 +1592,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På murken stubbe i granskog</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1618,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1748,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124204041</v>
+        <v>124189873</v>
       </c>
       <c r="B11" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,57 +1770,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637921</v>
+        <v>638016</v>
       </c>
       <c r="R11" t="n">
-        <v>6665671</v>
+        <v>6665594</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,12 +1847,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124204400</v>
+        <v>124232011</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1894,30 +1892,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1926,13 +1936,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637987</v>
+        <v>638028</v>
       </c>
       <c r="R12" t="n">
-        <v>6665598</v>
+        <v>6665609</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1959,24 +1969,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2162,17 +2162,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R14" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R15" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124205123</v>
+        <v>124204400</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637929</v>
+        <v>637987</v>
       </c>
       <c r="R2" t="n">
-        <v>6665530</v>
+        <v>6665598</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124232392</v>
+        <v>124189300</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638011</v>
+        <v>638050</v>
       </c>
       <c r="R3" t="n">
-        <v>6665601</v>
+        <v>6665625</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,9 +874,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124205801</v>
+        <v>124209310</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -933,20 +953,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637878</v>
+        <v>638018</v>
       </c>
       <c r="R4" t="n">
-        <v>6665615</v>
+        <v>6665626</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124204041</v>
+        <v>124189873</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,57 +1168,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637921</v>
+        <v>638016</v>
       </c>
       <c r="R6" t="n">
-        <v>6665671</v>
+        <v>6665594</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1245,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1397,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124204400</v>
+        <v>124232392</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,13 +1444,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637987</v>
+        <v>638011</v>
       </c>
       <c r="R8" t="n">
-        <v>6665598</v>
+        <v>6665601</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,24 +1477,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,7 +1507,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124209310</v>
+        <v>124205801</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,16 +1541,20 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638018</v>
+        <v>637878</v>
       </c>
       <c r="R9" t="n">
-        <v>6665626</v>
+        <v>6665615</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1594,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1610,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1636,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124189300</v>
+        <v>124205123</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,14 +1669,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638050</v>
+        <v>637929</v>
       </c>
       <c r="R10" t="n">
-        <v>6665625</v>
+        <v>6665530</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1715,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,12 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124189873</v>
+        <v>124232011</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,30 +1758,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1802,13 +1802,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638016</v>
+        <v>638028</v>
       </c>
       <c r="R11" t="n">
-        <v>6665594</v>
+        <v>6665609</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,24 +1835,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,7 +1870,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124232011</v>
+        <v>124204041</v>
       </c>
       <c r="B12" t="n">
         <v>95551</v>
@@ -1915,7 +1905,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1932,14 +1922,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638028</v>
+        <v>637921</v>
       </c>
       <c r="R12" t="n">
-        <v>6665609</v>
+        <v>6665671</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1969,14 +1959,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På murken stubbe i granskog</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2162,17 +2162,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R14" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R15" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124204400</v>
+        <v>124189300</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637987</v>
+        <v>638050</v>
       </c>
       <c r="R2" t="n">
-        <v>6665598</v>
+        <v>6665625</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124189300</v>
+        <v>124204041</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,45 +809,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638050</v>
+        <v>637921</v>
       </c>
       <c r="R3" t="n">
-        <v>6665625</v>
+        <v>6665671</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1036,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189769</v>
+        <v>124232392</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>96354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1064,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638030</v>
+        <v>638011</v>
       </c>
       <c r="R5" t="n">
-        <v>6665602</v>
+        <v>6665601</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,27 +1125,18 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124190637</v>
+        <v>124205123</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,25 +1289,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,17 +1317,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637893</v>
+        <v>637929</v>
       </c>
       <c r="R7" t="n">
-        <v>6665652</v>
+        <v>6665530</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,12 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124232392</v>
+        <v>124204400</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1406,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1444,13 +1438,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638011</v>
+        <v>637987</v>
       </c>
       <c r="R8" t="n">
-        <v>6665601</v>
+        <v>6665598</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,9 +1471,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1516,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124205801</v>
+        <v>124190637</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1551,13 +1560,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637878</v>
+        <v>637893</v>
       </c>
       <c r="R9" t="n">
-        <v>6665615</v>
+        <v>6665652</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,7 +1595,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,12 +1605,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124205123</v>
+        <v>124232011</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
+        <v>95551</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,45 +1650,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637929</v>
+        <v>638028</v>
       </c>
       <c r="R10" t="n">
-        <v>6665530</v>
+        <v>6665609</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,19 +1727,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:25</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124232011</v>
+        <v>124189769</v>
       </c>
       <c r="B11" t="n">
-        <v>95551</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,43 +1774,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1802,13 +1810,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638028</v>
+        <v>638030</v>
       </c>
       <c r="R11" t="n">
-        <v>6665609</v>
+        <v>6665602</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,14 +1843,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På murken stubbe i granskog</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1864,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1870,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124204041</v>
+        <v>124205801</v>
       </c>
       <c r="B12" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,57 +1894,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637921</v>
+        <v>637878</v>
       </c>
       <c r="R12" t="n">
-        <v>6665671</v>
+        <v>6665615</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2162,17 +2162,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R14" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R15" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189300</v>
+        <v>124209310</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -709,20 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638050</v>
+        <v>638018</v>
       </c>
       <c r="R2" t="n">
-        <v>6665625</v>
+        <v>6665626</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124204041</v>
+        <v>124205801</v>
       </c>
       <c r="B3" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,57 +804,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637921</v>
+        <v>637878</v>
       </c>
       <c r="R3" t="n">
-        <v>6665671</v>
+        <v>6665615</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124209310</v>
+        <v>124204400</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -965,16 +948,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638018</v>
+        <v>637987</v>
       </c>
       <c r="R4" t="n">
-        <v>6665626</v>
+        <v>6665598</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1006,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124232392</v>
+        <v>124189873</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,25 +1048,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1092,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638011</v>
+        <v>638016</v>
       </c>
       <c r="R5" t="n">
-        <v>6665601</v>
+        <v>6665594</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1125,9 +1113,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189873</v>
+        <v>124205123</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,25 +1170,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,17 +1198,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638016</v>
+        <v>637929</v>
       </c>
       <c r="R6" t="n">
-        <v>6665594</v>
+        <v>6665530</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124205123</v>
+        <v>124189300</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1287,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,14 +1315,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637929</v>
+        <v>638050</v>
       </c>
       <c r="R7" t="n">
-        <v>6665530</v>
+        <v>6665625</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1356,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124204400</v>
+        <v>124204041</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,45 +1409,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637987</v>
+        <v>637921</v>
       </c>
       <c r="R8" t="n">
-        <v>6665598</v>
+        <v>6665671</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1498,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1638,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124232011</v>
+        <v>124189769</v>
       </c>
       <c r="B10" t="n">
-        <v>95551</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,43 +1665,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,13 +1701,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638028</v>
+        <v>638030</v>
       </c>
       <c r="R10" t="n">
-        <v>6665609</v>
+        <v>6665602</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,14 +1734,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På murken stubbe i granskog</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,7 +1755,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1762,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124189769</v>
+        <v>124232392</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1778,31 +1789,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1810,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638030</v>
+        <v>638011</v>
       </c>
       <c r="R11" t="n">
-        <v>6665602</v>
+        <v>6665601</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1843,27 +1850,18 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1882,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124205801</v>
+        <v>124232011</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1894,30 +1892,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1926,13 +1936,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637878</v>
+        <v>638028</v>
       </c>
       <c r="R12" t="n">
-        <v>6665615</v>
+        <v>6665609</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1959,24 +1969,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,7 +2004,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124698226</v>
+        <v>124696996</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2038,23 +2038,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638166</v>
+        <v>638100</v>
       </c>
       <c r="R13" t="n">
-        <v>6665714</v>
+        <v>6665721</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,7 +2079,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,12 +2089,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,7 +2103,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2126,7 +2121,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124696996</v>
+        <v>124698226</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2160,19 +2155,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638100</v>
+        <v>638166</v>
       </c>
       <c r="R14" t="n">
-        <v>6665721</v>
+        <v>6665714</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2200,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2210,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,6 +2224,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124209310</v>
+        <v>124190637</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -709,19 +709,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638018</v>
+        <v>637893</v>
       </c>
       <c r="R2" t="n">
-        <v>6665626</v>
+        <v>6665652</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +778,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124205801</v>
+        <v>124232392</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637878</v>
+        <v>638011</v>
       </c>
       <c r="R3" t="n">
-        <v>6665615</v>
+        <v>6665601</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,24 +874,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124204400</v>
+        <v>124209310</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -948,20 +938,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637987</v>
+        <v>638018</v>
       </c>
       <c r="R4" t="n">
-        <v>6665598</v>
+        <v>6665626</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -993,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1003,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189873</v>
+        <v>124189769</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,31 +1033,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638016</v>
+        <v>638030</v>
       </c>
       <c r="R5" t="n">
-        <v>6665594</v>
+        <v>6665602</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1115,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1158,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124205123</v>
+        <v>124189300</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,25 +1153,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,14 +1181,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637929</v>
+        <v>638050</v>
       </c>
       <c r="R6" t="n">
-        <v>6665530</v>
+        <v>6665625</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1237,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124189300</v>
+        <v>124232011</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,30 +1275,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638050</v>
+        <v>638028</v>
       </c>
       <c r="R7" t="n">
-        <v>6665625</v>
+        <v>6665609</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,24 +1352,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124204041</v>
+        <v>124205123</v>
       </c>
       <c r="B8" t="n">
-        <v>95551</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,57 +1399,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637921</v>
+        <v>637929</v>
       </c>
       <c r="R8" t="n">
-        <v>6665671</v>
+        <v>6665530</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1498,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124190637</v>
+        <v>124204041</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,45 +1516,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637893</v>
+        <v>637921</v>
       </c>
       <c r="R9" t="n">
-        <v>6665652</v>
+        <v>6665671</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1595,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1605,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124189769</v>
+        <v>124189873</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,35 +1650,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1701,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638030</v>
+        <v>638016</v>
       </c>
       <c r="R10" t="n">
-        <v>6665602</v>
+        <v>6665594</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1736,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1727,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,6 +1741,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1773,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124232392</v>
+        <v>124204400</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1817,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638011</v>
+        <v>637987</v>
       </c>
       <c r="R11" t="n">
-        <v>6665601</v>
+        <v>6665598</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1850,9 +1837,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124232011</v>
+        <v>124205801</v>
       </c>
       <c r="B12" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,42 +1894,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1936,13 +1926,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638028</v>
+        <v>637878</v>
       </c>
       <c r="R12" t="n">
-        <v>6665609</v>
+        <v>6665615</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,14 +1959,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På murken stubbe i granskog</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,7 +2004,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124696996</v>
+        <v>124698226</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2038,19 +2038,23 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638100</v>
+        <v>638166</v>
       </c>
       <c r="R13" t="n">
-        <v>6665721</v>
+        <v>6665714</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2079,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2089,12 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,6 +2107,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2121,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124698226</v>
+        <v>124697608</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2155,20 +2160,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638166</v>
+        <v>638131</v>
       </c>
       <c r="R14" t="n">
-        <v>6665714</v>
+        <v>6665719</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2200,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2210,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,7 +2225,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R15" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2126,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2162,17 +2162,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R14" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R15" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2126,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2162,17 +2162,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R14" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R15" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124698226</v>
+        <v>124697608</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2038,20 +2038,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638166</v>
+        <v>638131</v>
       </c>
       <c r="R13" t="n">
-        <v>6665714</v>
+        <v>6665719</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2083,7 +2079,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,12 +2089,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,7 +2103,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2126,7 +2121,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124697608</v>
+        <v>124698226</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2160,16 +2155,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638131</v>
+        <v>638166</v>
       </c>
       <c r="R14" t="n">
-        <v>6665719</v>
+        <v>6665714</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2201,7 +2200,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2210,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,6 +2224,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124697608</v>
+        <v>124698226</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2038,16 +2038,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638131</v>
+        <v>638166</v>
       </c>
       <c r="R13" t="n">
-        <v>6665719</v>
+        <v>6665714</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2079,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2089,12 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,6 +2107,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2121,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124698226</v>
+        <v>124697608</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2155,20 +2160,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638166</v>
+        <v>638131</v>
       </c>
       <c r="R14" t="n">
-        <v>6665714</v>
+        <v>6665719</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2200,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2210,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,7 +2225,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2004,10 +2004,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124698226</v>
+        <v>124696996</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,23 +2038,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638166</v>
+        <v>638100</v>
       </c>
       <c r="R13" t="n">
-        <v>6665714</v>
+        <v>6665721</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,7 +2079,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,12 +2089,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,7 +2103,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2126,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124697608</v>
+        <v>124698226</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,16 +2155,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638131</v>
+        <v>638166</v>
       </c>
       <c r="R14" t="n">
-        <v>6665719</v>
+        <v>6665714</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2201,7 +2200,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2210,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,6 +2224,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R15" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124696996</v>
+        <v>124698226</v>
       </c>
       <c r="B13" t="n">
         <v>98269</v>
@@ -2038,19 +2038,23 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638100</v>
+        <v>638166</v>
       </c>
       <c r="R13" t="n">
-        <v>6665721</v>
+        <v>6665714</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2079,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2089,12 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,6 +2107,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2121,7 +2126,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124698226</v>
+        <v>124697608</v>
       </c>
       <c r="B14" t="n">
         <v>98269</v>
@@ -2155,20 +2160,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638166</v>
+        <v>638131</v>
       </c>
       <c r="R14" t="n">
-        <v>6665714</v>
+        <v>6665719</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2200,7 +2201,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2210,12 +2211,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,7 +2225,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B15" t="n">
         <v>98269</v>
@@ -2279,17 +2279,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R15" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13594-2025 artfynd.xlsx
+++ b/artfynd/A 13594-2025 artfynd.xlsx
@@ -2009,11 +2009,6 @@
       <c r="B13" t="n">
         <v>98269</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2126,16 +2121,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124697608</v>
+        <v>124696996</v>
       </c>
       <c r="B14" t="n">
         <v>98269</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2162,17 +2152,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638131</v>
+        <v>638100</v>
       </c>
       <c r="R14" t="n">
-        <v>6665719</v>
+        <v>6665721</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,7 +2191,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2211,12 +2201,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,16 +2233,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124696996</v>
+        <v>124697608</v>
       </c>
       <c r="B15" t="n">
         <v>98269</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2279,17 +2264,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638100</v>
+        <v>638131</v>
       </c>
       <c r="R15" t="n">
-        <v>6665721</v>
+        <v>6665719</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,7 +2303,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2328,12 +2313,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
